--- a/artfynd/A 31113-2025 artfynd.xlsx
+++ b/artfynd/A 31113-2025 artfynd.xlsx
@@ -1008,7 +1008,7 @@
         <v>136041196</v>
       </c>
       <c r="B5" t="n">
-        <v>96554</v>
+        <v>96557</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>136041562</v>
       </c>
       <c r="B6" t="n">
-        <v>91872</v>
+        <v>91881</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>136041712</v>
       </c>
       <c r="B7" t="n">
-        <v>89314</v>
+        <v>89316</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>136042167</v>
       </c>
       <c r="B11" t="n">
-        <v>99680</v>
+        <v>99683</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>136041541</v>
       </c>
       <c r="B13" t="n">
-        <v>98251</v>
+        <v>98254</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>136041496</v>
       </c>
       <c r="B17" t="n">
-        <v>99619</v>
+        <v>99622</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 31113-2025 artfynd.xlsx
+++ b/artfynd/A 31113-2025 artfynd.xlsx
@@ -1008,7 +1008,7 @@
         <v>136041196</v>
       </c>
       <c r="B5" t="n">
-        <v>96557</v>
+        <v>96558</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>136041562</v>
       </c>
       <c r="B6" t="n">
-        <v>91881</v>
+        <v>91882</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>136042167</v>
       </c>
       <c r="B11" t="n">
-        <v>99683</v>
+        <v>99684</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>136041541</v>
       </c>
       <c r="B13" t="n">
-        <v>98254</v>
+        <v>98255</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>136041496</v>
       </c>
       <c r="B17" t="n">
-        <v>99622</v>
+        <v>99623</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
